--- a/data/trans_camb/P1403-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1403-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,47</t>
+          <t>8,26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,4</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>6,26</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 3,28</t>
+          <t>-7,71; 3,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 3,67</t>
+          <t>-7,28; 4,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 12,34</t>
+          <t>2,31; 13,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 6,38</t>
+          <t>-5,25; 6,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 2,63</t>
+          <t>-8,64; 2,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 10,87</t>
+          <t>-1,89; 9,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 3,42</t>
+          <t>-5,09; 2,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 2,05</t>
+          <t>-6,47; 1,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 9,89</t>
+          <t>2,17; 9,87</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,96; 32,4</t>
+          <t>-48,16; 33,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-46,06; 36,17</t>
+          <t>-44,69; 38,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 123,21</t>
+          <t>15,38; 140,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,44; 57,33</t>
+          <t>-32,68; 60,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,4; 22,15</t>
+          <t>-49,04; 28,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 100,19</t>
+          <t>-10,65; 83,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,09; 28,48</t>
+          <t>-31,14; 25,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 17,05</t>
+          <t>-40,12; 13,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,65; 85,73</t>
+          <t>12,59; 85,03</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>7,03</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-1,54</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>2,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 10,98</t>
+          <t>2,47; 11,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 11,75</t>
+          <t>2,83; 11,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 11,19</t>
+          <t>2,49; 11,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 7,92</t>
+          <t>-2,36; 7,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 10,8</t>
+          <t>0,05; 10,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 2,65</t>
+          <t>-5,98; 2,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,86</t>
+          <t>1,56; 7,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 9,39</t>
+          <t>3,05; 9,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 5,79</t>
+          <t>-0,71; 5,75</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-9,06%</t>
+          <t>-8,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,01; 150,94</t>
+          <t>19,39; 144,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,06; 155,39</t>
+          <t>21,93; 151,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,31; 147,44</t>
+          <t>20,29; 153,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 52,98</t>
+          <t>-12,05; 50,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 73,87</t>
+          <t>-0,97; 70,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 19,08</t>
+          <t>-29,2; 17,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,57; 65,79</t>
+          <t>10,65; 65,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,53; 77,47</t>
+          <t>20,53; 84,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 48,21</t>
+          <t>-4,63; 47,5</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,78</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,32</t>
+          <t>3,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 10,13</t>
+          <t>-1,42; 9,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 5,74</t>
+          <t>-5,79; 5,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 11,97</t>
+          <t>0,47; 10,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 8,2</t>
+          <t>-5,12; 7,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,89; -0,2</t>
+          <t>-11,97; 0,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 6,4</t>
+          <t>-5,05; 5,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 7,31</t>
+          <t>-1,52; 7,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 1,46</t>
+          <t>-7,35; 0,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 7,15</t>
+          <t>-0,92; 6,76</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 82,93</t>
+          <t>-9,77; 84,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,24; 48,31</t>
+          <t>-33,75; 45,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 101,96</t>
+          <t>2,94; 98,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 46,35</t>
+          <t>-21,37; 43,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,5; -0,93</t>
+          <t>-50,17; 1,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 34,79</t>
+          <t>-19,98; 32,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 45,4</t>
+          <t>-7,88; 45,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 9,13</t>
+          <t>-35,7; 6,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 45,28</t>
+          <t>-5,39; 42,98</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>4,77</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>3,55</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>4,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 9,42</t>
+          <t>-2,17; 9,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 7,52</t>
+          <t>-2,65; 7,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 12,16</t>
+          <t>-0,69; 10,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 13,16</t>
+          <t>1,13; 12,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 7,01</t>
+          <t>-4,68; 7,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 5,92</t>
+          <t>-2,73; 7,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 9,76</t>
+          <t>1,23; 9,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 5,6</t>
+          <t>-2,31; 5,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 6,91</t>
+          <t>0,59; 8,26</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-2,32%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 77,06</t>
+          <t>-12,89; 80,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 63,72</t>
+          <t>-17,16; 66,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 96,57</t>
+          <t>-4,4; 89,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 80,49</t>
+          <t>5,31; 78,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,16; 42,88</t>
+          <t>-22,72; 44,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,84; 34,99</t>
+          <t>-12,07; 48,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,24; 64,33</t>
+          <t>6,56; 65,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 36,87</t>
+          <t>-12,23; 40,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 46,07</t>
+          <t>3,03; 56,55</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16,37</t>
+          <t>14,77</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,67</t>
+          <t>12,96</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15,68</t>
+          <t>13,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,88</t>
+          <t>1,13; 13,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 10,77</t>
+          <t>-0,84; 10,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,72; 22,67</t>
+          <t>8,43; 20,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,67; 20,01</t>
+          <t>4,41; 18,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 12,58</t>
+          <t>-1,96; 12,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,84; 21,11</t>
+          <t>6,52; 18,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,7; 14,69</t>
+          <t>4,1; 14,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 9,71</t>
+          <t>-0,17; 9,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10,79; 20,24</t>
+          <t>9,18; 17,93</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>209,4%</t>
+          <t>189,0%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>138,3%</t>
+          <t>123,06%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8,65; 253,68</t>
+          <t>6,76; 254,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 202,17</t>
+          <t>-10,9; 219,19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85,78; 460,39</t>
+          <t>71,49; 407,73</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16,16; 174,58</t>
+          <t>23,67; 176,4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 114,39</t>
+          <t>-12,26; 111,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,73; 197,18</t>
+          <t>33,69; 168,09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,32; 155,39</t>
+          <t>30,66; 153,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,33; 103,87</t>
+          <t>-1,53; 102,85</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>76,29; 225,77</t>
+          <t>66,56; 206,14</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11,95</t>
+          <t>11,47</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,63</t>
+          <t>4,8</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8,31</t>
+          <t>8,13</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,88; 14,58</t>
+          <t>1,3; 14,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 4,23</t>
+          <t>-8,65; 4,12</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,01; 18,28</t>
+          <t>4,72; 17,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 11,09</t>
+          <t>-3,52; 10,35</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 4,56</t>
+          <t>-7,75; 5,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 10,76</t>
+          <t>-0,89; 10,35</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,14; 10,43</t>
+          <t>0,98; 10,79</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 3,18</t>
+          <t>-6,1; 3,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,22; 12,55</t>
+          <t>3,89; 12,15</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>47,63%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4,89; 119,04</t>
+          <t>5,73; 120,34</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-40,45; 36,65</t>
+          <t>-43,74; 34,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>31,41; 157,82</t>
+          <t>25,42; 146,35</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 76,28</t>
+          <t>-16,7; 63,69</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-38,98; 30,61</t>
+          <t>-35,34; 35,42</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 72,09</t>
+          <t>-4,32; 65,0</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,11; 71,48</t>
+          <t>4,48; 71,09</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 22,34</t>
+          <t>-31,76; 20,9</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>21,49; 85,66</t>
+          <t>20,04; 82,54</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>4,02</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,47</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>14,58</t>
+          <t>3,99</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,49; 9,21</t>
+          <t>0,26; 8,86</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 4,12</t>
+          <t>-3,81; 4,01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 7,44</t>
+          <t>0,19; 8,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,14; 9,88</t>
+          <t>1,3; 10,08</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 1,1</t>
+          <t>-7,12; 1,11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,02; 52,82</t>
+          <t>0,26; 8,03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,24</t>
+          <t>2,35; 8,34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 1,23</t>
+          <t>-4,38; 1,23</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,47; 43,51</t>
+          <t>0,84; 6,75</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>129,33%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2,68; 73,86</t>
+          <t>1,37; 70,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 33,94</t>
+          <t>-22,98; 31,86</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 61,29</t>
+          <t>1,23; 66,95</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5,66; 64,11</t>
+          <t>6,39; 68,18</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-36,87; 6,64</t>
+          <t>-36,98; 7,82</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,21; 330,54</t>
+          <t>1,41; 53,96</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,21; 57,47</t>
+          <t>13,11; 56,12</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-25,13; 8,77</t>
+          <t>-26,12; 8,38</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>15,29; 299,73</t>
+          <t>4,92; 47,66</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>3,24</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,63</t>
+          <t>6,59</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>4,95</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 4,88</t>
+          <t>-2,98; 4,48</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 6,44</t>
+          <t>-0,71; 6,66</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 5,25</t>
+          <t>-0,65; 6,75</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 6,5</t>
+          <t>-0,95; 6,22</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,43; 9,26</t>
+          <t>1,18; 8,95</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,09; 11,51</t>
+          <t>2,84; 10,01</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,43</t>
+          <t>-0,64; 4,56</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,7</t>
+          <t>1,48; 6,87</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 6,69</t>
+          <t>2,6; 7,33</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-4,57%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 41,24</t>
+          <t>-19,2; 37,42</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 54,36</t>
+          <t>-4,36; 57,89</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-55,09; 41,54</t>
+          <t>-4,01; 56,56</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 50,66</t>
+          <t>-5,93; 50,54</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,52; 72,29</t>
+          <t>7,18; 73,14</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,87; 93,92</t>
+          <t>16,24; 83,36</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 34,71</t>
+          <t>-4,17; 36,44</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>9,35; 52,31</t>
+          <t>9,46; 54,19</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 49,86</t>
+          <t>16,73; 57,28</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>6,11</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,22</t>
+          <t>3,99</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>5,05</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,46</t>
+          <t>2,14; 5,56</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,8</t>
+          <t>0,33; 3,69</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,07</t>
+          <t>4,47; 7,81</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,0</t>
+          <t>2,11; 5,87</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,64</t>
+          <t>-1,12; 2,82</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,15; 23,52</t>
+          <t>2,39; 5,64</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,16</t>
+          <t>2,66; 5,06</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,7</t>
+          <t>0,09; 2,64</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,71; 14,76</t>
+          <t>3,7; 6,18</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>13,87; 45,45</t>
+          <t>15,37; 45,57</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3,32; 31,33</t>
+          <t>2,37; 30,1</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>8,39; 56,92</t>
+          <t>32,82; 65,28</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11,71; 37,81</t>
+          <t>11,97; 36,64</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 16,6</t>
+          <t>-6,33; 17,72</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>18,13; 138,87</t>
+          <t>13,33; 35,13</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>16,9; 36,11</t>
+          <t>17,16; 35,48</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0,81; 18,68</t>
+          <t>0,5; 18,23</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>23,88; 97,5</t>
+          <t>23,45; 43,09</t>
         </is>
       </c>
     </row>
